--- a/光伏配储项目/电价数据/2026/惠炼站.xlsx
+++ b/光伏配储项目/电价数据/2026/惠炼站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.66692</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8915599999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60293</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.64703</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.6592100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43736</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42517</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43237</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5127999999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.17693</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.19532</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.17541</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.24066</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05896</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15624</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.23595</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23771</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24268</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.76487</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.47934</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.5710299999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.65366</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.7126699999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72723</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.3508</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43012</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65528</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.05478</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.66035</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.3957</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.58398</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.25739</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.47135</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.47131</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.7283</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.63359</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.92796</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.45005</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.18643</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86613</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79423</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75439</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47734</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46586</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41471</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42419</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7019500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74875</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86386</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9055299999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5087200000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.4979</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49811</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46319</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.74148</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59972</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.69537</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5089399999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.55972</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.83373</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.04796</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.92408</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.87851</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8067799999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.20007</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.0502</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49296</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5739099999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.53213</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.53428</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8769199999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6105700000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8188200000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.9701000000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.30195</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16554</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.94355</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.35154</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.25524</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.41285</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.19398</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.24003</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79802</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.13113</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.89507</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16288</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.12468</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.15118</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9494600000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.80589</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8254900000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42629</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33438</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50348</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48333</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4817</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46819</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44189</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43493</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20493</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.26301</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.17298</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.53071</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.63188</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5910599999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.88261</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.53085</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.66987</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.76319</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.84919</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52454</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5114300000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7834800000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6852999999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64195</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.62497</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49941</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.60661</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.59026</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.24015</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61121</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.87288</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5172</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57601</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.78501</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8019400000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.05752</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.56368</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.51763</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.65066</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6029500000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.77486</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56213</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.98717</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.74276</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5726100000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.63737</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45461</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34168</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51616</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44586</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.45814</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.5569299999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.5382400000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.49631</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.4602</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7052</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.55359</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.50336</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5935499999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4866</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.54153</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.55923</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.51459</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.86803</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.48441</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.52859</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.75886</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6275599999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.9137000000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.67475</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.61913</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.53786</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4909</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.43074</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31112</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.23207</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14924</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.15071</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.22951</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.23973</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22058</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.07912000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.15841</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.10281</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01148</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26662</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38158</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33424</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.49073</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.23363</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.14698</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28949</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.24891</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10332</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04391</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04479</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01294</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21178</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05204</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19931</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.16006</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.13471</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06592000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06415000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32568</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.30291</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78499</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8742300000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.9269299999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.66996</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77297</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39639</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56657</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.66784</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87048</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4617</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.51091</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7301599999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.48675</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83833</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.5315700000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.54222</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5804900000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.72999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28885</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33871</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9079199999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.22285</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19491</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.2629</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.24915</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.26947</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.42254</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.4416</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.82343</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3961</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.09415</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.65999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7491599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6129600000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46961</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4113</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47221</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.48347</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.10922</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24517</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02378</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25571</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.50092</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7021000000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.28254</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29128</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.24546</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.25273</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.25859</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.23478</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26618</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.22726</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.22769</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.28545</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.13817</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.24269</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.14025</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26877</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.18341</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.22345</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.23384</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23533</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.24882</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.25095</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23916</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42973</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.31518</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30212</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.5135700000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.5793400000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.54616</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.61488</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.68043</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.69396</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.50249</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.33287</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.30789</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.59496</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.8484700000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.54615</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.67735</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.65828</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.5340900000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.62778</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.55037</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.59087</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.57078</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.88598</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.85137</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.55201</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.73088</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.09794</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.88493</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.65996</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.81347</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.7410599999999999</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.72504</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.96833</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.70416</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.71954</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.72563</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.6361100000000001</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.84211</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.53644</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.50991</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.48378</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.56526</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.5081600000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.49603</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.87859</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.62142</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.59666</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.57838</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.85611</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.52996</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.52011</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.51057</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.44437</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49436</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29112</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.26635</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.25849</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.26002</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.26491</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.25809</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.24602</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.5275599999999999</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.48145</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3345</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.17045</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.49111</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6433099999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.32616</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.32047</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.76551</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.5200900000000001</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.50436</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.44335</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.55533</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.46398</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.5435599999999999</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.74066</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.49533</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.46859</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.5992999999999999</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.49393</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.5724400000000001</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.73107</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.13214</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.81704</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.79769</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.75528</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.93011</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5734199999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.92272</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5847100000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.03957</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.05809</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.5523400000000001</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.8058500000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.72725</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.51642</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33709</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46024</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.51944</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.5107</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.55479</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.60226</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.6390800000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.81465</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.71817</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.48729</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.53051</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.48946</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.7380800000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.97941</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.49511</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.57874</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.51022</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.57657</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6640499999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.48631</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5771000000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59017</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.57111</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7581100000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61027</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6574099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.57696</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.39262</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.18604</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36443</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.45386</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.56201</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5206900000000001</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5248200000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.73719</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.21648</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.28323</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.55499</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.17365</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.25808</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.27266</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.16564</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.24334</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.24992</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.25027</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.25412</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.16061</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.15997</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.14735</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.24943</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.13996</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27659</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.21146</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.26744</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28435</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27215</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24971</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.31396</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.26927</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.25328</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.2858</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.43465</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.18644</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.24953</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.14678</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.26243</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.16959</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.1421</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.14674</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.14674</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.25076</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.13954</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.14674</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.14695</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.24279</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.09949</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.14383</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00532</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14225</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01589</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04081</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04825</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02929</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00074</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03853</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02173</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03635</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26427</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.15008</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30866</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5881900000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.51916</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25607</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25392</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15595</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25173</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23706</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.15713</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.12809</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15052</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.15454</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.13894</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.17865</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.18689</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.20241</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.15439</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.64285</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87012</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85581</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11643</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.13787</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.09473000000000001</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.03189</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.27369</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00026</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06742000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25458</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.21348</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6984400000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.6173099999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.65279</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.15855</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98072</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.62303</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.66574</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83357</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8317899999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83608</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9337300000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.61326</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6617499999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.6195499999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34284</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.4775</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.48558</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.40391</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.25311</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.25688</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.16419</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40889</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.59942</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42698</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32362</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36438</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.71238</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.46516</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.48968</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.49141</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.68076</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.50293</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48598</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.1973</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.91365</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.77112</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.59711</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.7329600000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.64078</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.61226</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.9664700000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.6774</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.66689</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.50937</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.5111</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.57529</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22451</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3414</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.59182</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40372</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5056700000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.65426</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.46032</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.6568099999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.14275</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.57062</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.7742899999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5866699999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.92353</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7962</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.03971</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.94145</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.85354</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.73456</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.52626</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34585</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.14846</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.7394400000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.60176</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.64398</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.43004</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.30478</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.74639</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.61051</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.0352</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.49547</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.38906</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.8262699999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.58013</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.7351799999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.39458</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.57316</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.62673</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5649299999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.62758</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.5622999999999999</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36684</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.45519</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6904400000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.41346</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.46595</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.88632</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.65413</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.53263</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.89595</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.52727</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.48666</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.6170599999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35175</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9749800000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5315800000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.52451</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.61633</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5639</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40177</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.65363</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.77777</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.6182000000000001</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.52364</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5524199999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35226</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17575</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14543</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19817</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14303</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04552</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12119</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22552</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14842</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19306</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22633</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15169</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15346</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19571</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.50456</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.74676</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46493</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.43545</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.42217</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37935</v>
       </c>
     </row>
   </sheetData>
